--- a/data/extracted/inventory-receipts/REP CONTENEDOR PERUANA 200 28.XLSX
+++ b/data/extracted/inventory-receipts/REP CONTENEDOR PERUANA 200 28.XLSX
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB57EC89-AFE7-4801-9416-7602688DB8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9135"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1682,7 +1695,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -1723,12 +1736,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2008,50 +2020,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L272"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -2089,12 +2101,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -2132,7 +2144,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -2170,7 +2182,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -2208,7 +2220,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -2246,7 +2258,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -2284,7 +2296,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -2322,7 +2334,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -2360,7 +2372,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -2398,7 +2410,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -2436,7 +2448,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -2474,7 +2486,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -2512,7 +2524,7 @@
         <v>20.350000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -2550,7 +2562,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -2588,7 +2600,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -2626,7 +2638,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -2664,7 +2676,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -2702,7 +2714,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -2740,7 +2752,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2778,7 +2790,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2816,7 +2828,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -2854,7 +2866,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -2892,7 +2904,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -2930,7 +2942,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -2968,7 +2980,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
@@ -3006,7 +3018,7 @@
         <v>20.45</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -3044,7 +3056,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -3082,7 +3094,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -3120,7 +3132,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -3158,7 +3170,7 @@
         <v>20.45</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -3196,7 +3208,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -3234,7 +3246,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -3272,7 +3284,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -3310,7 +3322,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -3348,7 +3360,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -3386,7 +3398,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -3424,7 +3436,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -3462,7 +3474,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -3500,7 +3512,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -3538,7 +3550,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -3576,7 +3588,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -3614,7 +3626,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -3652,7 +3664,7 @@
         <v>20.25</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -3690,7 +3702,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -3728,7 +3740,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -3766,7 +3778,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -3804,7 +3816,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -3842,7 +3854,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -3880,7 +3892,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -3918,7 +3930,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -3956,7 +3968,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -3994,7 +4006,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -4032,7 +4044,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -4070,7 +4082,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -4108,7 +4120,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -4146,7 +4158,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -4184,7 +4196,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -4222,7 +4234,7 @@
         <v>19.55</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>19</v>
       </c>
@@ -4260,7 +4272,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -4298,7 +4310,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>19</v>
       </c>
@@ -4336,7 +4348,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>19</v>
       </c>
@@ -4374,7 +4386,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
@@ -4412,7 +4424,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -4450,7 +4462,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -4488,7 +4500,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
@@ -4526,7 +4538,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -4564,7 +4576,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>19</v>
       </c>
@@ -4602,7 +4614,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -4640,7 +4652,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>19</v>
       </c>
@@ -4678,7 +4690,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -4716,7 +4728,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>19</v>
       </c>
@@ -4754,7 +4766,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -4792,7 +4804,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
@@ -4830,7 +4842,7 @@
         <v>20.149999999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
@@ -4868,7 +4880,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
@@ -4906,7 +4918,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -4944,7 +4956,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>19</v>
       </c>
@@ -4982,7 +4994,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -5020,7 +5032,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>19</v>
       </c>
@@ -5058,7 +5070,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -5096,7 +5108,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>19</v>
       </c>
@@ -5134,7 +5146,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>19</v>
       </c>
@@ -5172,7 +5184,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -5210,7 +5222,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -5248,7 +5260,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>19</v>
       </c>
@@ -5286,7 +5298,7 @@
         <v>21.15</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>19</v>
       </c>
@@ -5324,7 +5336,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -5362,7 +5374,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>19</v>
       </c>
@@ -5400,7 +5412,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>19</v>
       </c>
@@ -5438,7 +5450,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
@@ -5476,7 +5488,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>19</v>
       </c>
@@ -5514,7 +5526,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>19</v>
       </c>
@@ -5552,7 +5564,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>19</v>
       </c>
@@ -5590,7 +5602,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>19</v>
       </c>
@@ -5628,7 +5640,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -5666,7 +5678,7 @@
         <v>20.45</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>19</v>
       </c>
@@ -5704,7 +5716,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>19</v>
       </c>
@@ -5742,7 +5754,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>19</v>
       </c>
@@ -5780,7 +5792,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>19</v>
       </c>
@@ -5818,7 +5830,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>19</v>
       </c>
@@ -5856,7 +5868,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
@@ -5894,7 +5906,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -5932,7 +5944,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>19</v>
       </c>
@@ -5970,7 +5982,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>19</v>
       </c>
@@ -6008,7 +6020,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -6046,7 +6058,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>19</v>
       </c>
@@ -6084,7 +6096,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>19</v>
       </c>
@@ -6122,7 +6134,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>19</v>
       </c>
@@ -6160,7 +6172,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>19</v>
       </c>
@@ -6198,7 +6210,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>19</v>
       </c>
@@ -6236,7 +6248,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>19</v>
       </c>
@@ -6274,7 +6286,7 @@
         <v>21.55</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -6312,7 +6324,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>19</v>
       </c>
@@ -6350,7 +6362,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>19</v>
       </c>
@@ -6388,7 +6400,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
@@ -6426,7 +6438,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>19</v>
       </c>
@@ -6464,7 +6476,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>19</v>
       </c>
@@ -6502,7 +6514,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>19</v>
       </c>
@@ -6540,7 +6552,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>19</v>
       </c>
@@ -6578,7 +6590,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>19</v>
       </c>
@@ -6616,7 +6628,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>19</v>
       </c>
@@ -6654,7 +6666,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>19</v>
       </c>
@@ -6692,7 +6704,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>19</v>
       </c>
@@ -6730,7 +6742,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>19</v>
       </c>
@@ -6768,7 +6780,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>19</v>
       </c>
@@ -6806,7 +6818,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>19</v>
       </c>
@@ -6844,7 +6856,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>19</v>
       </c>
@@ -6882,7 +6894,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>19</v>
       </c>
@@ -6920,7 +6932,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>19</v>
       </c>
@@ -6958,7 +6970,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>19</v>
       </c>
@@ -6996,7 +7008,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>19</v>
       </c>
@@ -7034,7 +7046,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>19</v>
       </c>
@@ -7072,7 +7084,7 @@
         <v>20.45</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>19</v>
       </c>
@@ -7110,7 +7122,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>19</v>
       </c>
@@ -7148,7 +7160,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>19</v>
       </c>
@@ -7186,7 +7198,7 @@
         <v>20.149999999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>19</v>
       </c>
@@ -7224,7 +7236,7 @@
         <v>20.149999999999999</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>19</v>
       </c>
@@ -7262,7 +7274,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>19</v>
       </c>
@@ -7300,7 +7312,7 @@
         <v>21.15</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>19</v>
       </c>
@@ -7338,7 +7350,7 @@
         <v>19.55</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>19</v>
       </c>
@@ -7376,7 +7388,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>19</v>
       </c>
@@ -7414,7 +7426,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>19</v>
       </c>
@@ -7452,7 +7464,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>19</v>
       </c>
@@ -7490,7 +7502,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>19</v>
       </c>
@@ -7528,7 +7540,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>19</v>
       </c>
@@ -7566,7 +7578,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>19</v>
       </c>
@@ -7604,7 +7616,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>19</v>
       </c>
@@ -7642,7 +7654,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>19</v>
       </c>
@@ -7680,7 +7692,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>19</v>
       </c>
@@ -7718,7 +7730,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>19</v>
       </c>
@@ -7756,7 +7768,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>19</v>
       </c>
@@ -7794,7 +7806,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>19</v>
       </c>
@@ -7832,7 +7844,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>19</v>
       </c>
@@ -7870,7 +7882,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>19</v>
       </c>
@@ -7908,7 +7920,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>19</v>
       </c>
@@ -7946,7 +7958,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>19</v>
       </c>
@@ -7984,7 +7996,7 @@
         <v>21.35</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>19</v>
       </c>
@@ -8022,7 +8034,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>19</v>
       </c>
@@ -8060,7 +8072,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>19</v>
       </c>
@@ -8098,7 +8110,7 @@
         <v>20.25</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>19</v>
       </c>
@@ -8136,7 +8148,7 @@
         <v>21.15</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>19</v>
       </c>
@@ -8174,7 +8186,7 @@
         <v>21.35</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>19</v>
       </c>
@@ -8212,7 +8224,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>19</v>
       </c>
@@ -8250,7 +8262,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>19</v>
       </c>
@@ -8288,7 +8300,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>19</v>
       </c>
@@ -8326,7 +8338,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>19</v>
       </c>
@@ -8364,7 +8376,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>19</v>
       </c>
@@ -8402,7 +8414,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>19</v>
       </c>
@@ -8440,7 +8452,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>19</v>
       </c>
@@ -8478,7 +8490,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>19</v>
       </c>
@@ -8516,7 +8528,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>19</v>
       </c>
@@ -8554,7 +8566,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>19</v>
       </c>
@@ -8592,7 +8604,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>19</v>
       </c>
@@ -8630,7 +8642,7 @@
         <v>21.15</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>19</v>
       </c>
@@ -8668,7 +8680,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>19</v>
       </c>
@@ -8706,7 +8718,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>19</v>
       </c>
@@ -8744,7 +8756,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>19</v>
       </c>
@@ -8782,7 +8794,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>19</v>
       </c>
@@ -8820,7 +8832,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>19</v>
       </c>
@@ -8858,7 +8870,7 @@
         <v>18.149999999999999</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>19</v>
       </c>
@@ -8896,7 +8908,7 @@
         <v>21.15</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>19</v>
       </c>
@@ -8934,7 +8946,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>19</v>
       </c>
@@ -8972,7 +8984,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>19</v>
       </c>
@@ -9010,7 +9022,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>19</v>
       </c>
@@ -9048,7 +9060,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>19</v>
       </c>
@@ -9086,7 +9098,7 @@
         <v>20.350000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>19</v>
       </c>
@@ -9124,7 +9136,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>19</v>
       </c>
@@ -9162,7 +9174,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>19</v>
       </c>
@@ -9200,7 +9212,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>19</v>
       </c>
@@ -9238,7 +9250,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>19</v>
       </c>
@@ -9276,7 +9288,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>19</v>
       </c>
@@ -9314,7 +9326,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>19</v>
       </c>
@@ -9352,7 +9364,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>19</v>
       </c>
@@ -9390,7 +9402,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>19</v>
       </c>
@@ -9428,7 +9440,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>19</v>
       </c>
@@ -9466,7 +9478,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>19</v>
       </c>
@@ -9504,7 +9516,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>19</v>
       </c>
@@ -9542,7 +9554,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>19</v>
       </c>
@@ -9580,7 +9592,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>19</v>
       </c>
@@ -9618,7 +9630,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>19</v>
       </c>
@@ -9656,7 +9668,7 @@
         <v>21.15</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>19</v>
       </c>
@@ -9694,7 +9706,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>19</v>
       </c>
@@ -9732,7 +9744,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>19</v>
       </c>
@@ -9770,7 +9782,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>19</v>
       </c>
@@ -9808,7 +9820,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>19</v>
       </c>
@@ -9846,7 +9858,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>19</v>
       </c>
@@ -9884,7 +9896,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>19</v>
       </c>
@@ -9922,7 +9934,7 @@
         <v>18.350000000000001</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>19</v>
       </c>
@@ -9960,7 +9972,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>19</v>
       </c>
@@ -9998,7 +10010,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>19</v>
       </c>
@@ -10036,7 +10048,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>19</v>
       </c>
@@ -10074,7 +10086,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>19</v>
       </c>
@@ -10112,7 +10124,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>19</v>
       </c>
@@ -10150,7 +10162,7 @@
         <v>20.350000000000001</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>19</v>
       </c>
@@ -10188,7 +10200,7 @@
         <v>21.55</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>19</v>
       </c>
@@ -10226,7 +10238,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>19</v>
       </c>
@@ -10264,7 +10276,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>19</v>
       </c>
@@ -10302,7 +10314,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>19</v>
       </c>
@@ -10340,7 +10352,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>19</v>
       </c>
@@ -10378,7 +10390,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>19</v>
       </c>
@@ -10416,7 +10428,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>19</v>
       </c>
@@ -10454,7 +10466,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>19</v>
       </c>
@@ -10492,7 +10504,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>19</v>
       </c>
@@ -10530,7 +10542,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>19</v>
       </c>
@@ -10568,7 +10580,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>19</v>
       </c>
@@ -10606,7 +10618,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>19</v>
       </c>
@@ -10644,7 +10656,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>19</v>
       </c>
@@ -10682,7 +10694,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>19</v>
       </c>
@@ -10720,7 +10732,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>19</v>
       </c>
@@ -10758,7 +10770,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>19</v>
       </c>
@@ -10796,7 +10808,7 @@
         <v>18.45</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>19</v>
       </c>
@@ -10834,7 +10846,7 @@
         <v>20.149999999999999</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>19</v>
       </c>
@@ -10872,7 +10884,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>19</v>
       </c>
@@ -10910,7 +10922,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>19</v>
       </c>
@@ -10948,7 +10960,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>19</v>
       </c>
@@ -10986,7 +10998,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>19</v>
       </c>
@@ -11024,7 +11036,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>19</v>
       </c>
@@ -11062,7 +11074,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>19</v>
       </c>
@@ -11100,7 +11112,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>19</v>
       </c>
@@ -11138,7 +11150,7 @@
         <v>20.25</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>19</v>
       </c>
@@ -11176,7 +11188,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>19</v>
       </c>
@@ -11214,7 +11226,7 @@
         <v>20.45</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>19</v>
       </c>
@@ -11252,7 +11264,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>19</v>
       </c>
@@ -11290,7 +11302,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>19</v>
       </c>
@@ -11328,7 +11340,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>19</v>
       </c>
@@ -11366,7 +11378,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>19</v>
       </c>
@@ -11404,7 +11416,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>19</v>
       </c>
@@ -11442,7 +11454,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>19</v>
       </c>
@@ -11480,7 +11492,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>19</v>
       </c>
@@ -11518,7 +11530,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>19</v>
       </c>
@@ -11556,7 +11568,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>19</v>
       </c>
@@ -11594,7 +11606,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>19</v>
       </c>
@@ -11632,7 +11644,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>19</v>
       </c>
@@ -11670,7 +11682,7 @@
         <v>20.149999999999999</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>19</v>
       </c>
@@ -11708,7 +11720,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>19</v>
       </c>
@@ -11746,7 +11758,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>19</v>
       </c>
@@ -11784,7 +11796,7 @@
         <v>21.15</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>19</v>
       </c>
@@ -11822,7 +11834,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>19</v>
       </c>
@@ -11860,7 +11872,7 @@
         <v>21.45</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>19</v>
       </c>
@@ -11898,7 +11910,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>19</v>
       </c>
@@ -11936,7 +11948,7 @@
         <v>20.45</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>19</v>
       </c>
@@ -11974,7 +11986,7 @@
         <v>20.45</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F267" s="1" t="s">
         <v>545</v>
       </c>
@@ -11994,7 +12006,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F268" s="1" t="s">
         <v>543</v>
       </c>
@@ -12011,7 +12023,7 @@
         <v>5376.1000000000022</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F269" s="1" t="s">
         <v>545</v>
       </c>
@@ -12031,7 +12043,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>547</v>
       </c>
@@ -12069,7 +12081,7 @@
         <v>322.58999999999997</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F272" s="1" t="s">
         <v>545</v>
       </c>
@@ -12093,4 +12105,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18B7B9FC-7A11-4BFA-B8CC-17689713502A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>47502</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>